--- a/apps/web/public/templates/12_الأجازات_الرسمية.xlsx
+++ b/apps/web/public/templates/12_الأجازات_الرسمية.xlsx
@@ -1562,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"الأجازات": [["", "عيد العمال"]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/apps/web/public/templates/12_الأجازات_الرسمية.xlsx
+++ b/apps/web/public/templates/12_الأجازات_الرسمية.xlsx
@@ -1441,7 +1441,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم تاريخ (يوم/شهر/سنة)" type="date" operator="greaterThan">
+    <dataValidation sqref="A3:A5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال تاريخ بصيغة يوم/شهر/سنة" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -1464,21 +1464,21 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>قالب الأجازات الرسمية</t>
+          <t>نموذج العطلات الرسمية</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>الغرض: الأيام اللي مش بتتحسب في الـ SLA (غير الجمعة والسبت).</t>
+          <t>الغرض: الأيام غير المحتسبة ضمن المدة المستهدفة (SLA)، بالإضافة إلى يومي الجمعة والسبت.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>مين بيرفعه: فريق المتابعة PMO.</t>
+          <t>الجهة المسؤولة عن الرفع: مكتب إدارة المشروعات (PMO).</t>
         </is>
       </c>
     </row>
@@ -1488,14 +1488,14 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>• كل يوم في صف.</t>
+          <t>• يُسجَّل كل يوم في صف مستقل.</t>
         </is>
       </c>
     </row>
@@ -1505,49 +1505,49 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/templates/12_الأجازات_الرسمية.xlsx
+++ b/apps/web/public/templates/12_الأجازات_الرسمية.xlsx
@@ -547,7 +547,7 @@
       <c r="A3" s="3" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>عيد العمال</t>
+          <t>مثال — عيد العمال</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"الأجازات": [["", "عيد العمال"]]}</t>
+          <t>{"الأجازات": [["", "مثال — عيد العمال"]]}</t>
         </is>
       </c>
     </row>
